--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_individual_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_individual_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008415679646344133</v>
       </c>
       <c r="C2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>9800094</v>
+        <v>4772423</v>
       </c>
       <c r="L2" t="n">
-        <v>6232641</v>
+        <v>2981114</v>
       </c>
       <c r="M2" t="n">
-        <v>1672339</v>
+        <v>776488</v>
       </c>
       <c r="N2" t="n">
-        <v>107029</v>
+        <v>43653</v>
       </c>
       <c r="O2" t="n">
-        <v>966416</v>
+        <v>458353</v>
       </c>
       <c r="P2" t="n">
-        <v>369299</v>
+        <v>177698</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999974370002747</v>
+        <v>0.9999958872795105</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9779650568962097</v>
+        <v>0.9564840197563171</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9341951608657837</v>
+        <v>0.8849969506263733</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9240912199020386</v>
+        <v>0.8684829473495483</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8448968529701233</v>
+        <v>0.6957873106002808</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9456412196159363</v>
+        <v>0.8961659073829651</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9660406708717346</v>
+        <v>0.9339107275009155</v>
       </c>
       <c r="X2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567450881004333</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112150073051453</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582985401153564</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627530455589294</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020664095878601</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -795,16 +795,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9800094</v>
+        <v>4772423</v>
       </c>
       <c r="E3" t="n">
-        <v>270566</v>
+        <v>259361</v>
       </c>
       <c r="F3" t="n">
-        <v>1859</v>
+        <v>1838</v>
       </c>
       <c r="G3" t="n">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H3" t="n">
         <v>83</v>
@@ -813,109 +813,109 @@
         <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>20033212</v>
+        <v>10016596</v>
       </c>
       <c r="K3" t="n">
-        <v>22365354</v>
+        <v>11078337</v>
       </c>
       <c r="L3" t="n">
-        <v>25705502</v>
+        <v>12682859</v>
       </c>
       <c r="M3" t="n">
-        <v>30658661</v>
+        <v>15280202</v>
       </c>
       <c r="N3" t="n">
-        <v>32461483</v>
+        <v>16221450</v>
       </c>
       <c r="O3" t="n">
-        <v>31585889</v>
+        <v>15767520</v>
       </c>
       <c r="P3" t="n">
-        <v>32259673</v>
+        <v>16123743</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9729037284851074</v>
+        <v>0.9480119347572327</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9567086100578308</v>
+        <v>0.9146336913108826</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8975791931152344</v>
+        <v>0.8333097100257874</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6010535359382629</v>
+        <v>0.4901306927204132</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9495538473129272</v>
+        <v>0.9005448222160339</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9553842544555664</v>
+        <v>0.9193717241287231</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>395630</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>17032</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13547</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20033244</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22150033</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25566849</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30532165</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32421126</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31541812</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32246147</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576732516288757</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100743532180786</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578290939331055</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66222083568573</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016799926757812</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>206145</v>
+        <v>202676</v>
       </c>
       <c r="E4" t="n">
-        <v>6232641</v>
+        <v>2981114</v>
       </c>
       <c r="F4" t="n">
-        <v>73648</v>
+        <v>73334</v>
       </c>
       <c r="G4" t="n">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="H4" t="n">
         <v>1167</v>
@@ -947,109 +947,109 @@
         <v>36</v>
       </c>
       <c r="J4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K4" t="n">
-        <v>220810</v>
+        <v>217125</v>
       </c>
       <c r="L4" t="n">
-        <v>439028</v>
+        <v>387388</v>
       </c>
       <c r="M4" t="n">
-        <v>137373</v>
+        <v>117586</v>
       </c>
       <c r="N4" t="n">
-        <v>19648</v>
+        <v>19086</v>
       </c>
       <c r="O4" t="n">
-        <v>55553</v>
+        <v>53107</v>
       </c>
       <c r="P4" t="n">
-        <v>12982</v>
+        <v>12575</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999987483024597</v>
+        <v>0.9999979138374329</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9754278063774109</v>
+        <v>0.9522291421890259</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9453179240226746</v>
+        <v>0.8995712399482727</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9106423258781433</v>
+        <v>0.8505327701568604</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7024144530296326</v>
+        <v>0.5751270055770874</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9475935101509094</v>
+        <v>0.8983500599861145</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9606829881668091</v>
+        <v>0.9265841841697693</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>407180</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165287</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10949</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>436131</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>577681</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263869</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>60005</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99630</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572089314460754</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106443524360657</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580637574195862</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624868512153625</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018731117248535</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,19 +1059,19 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>8459</v>
+        <v>8344</v>
       </c>
       <c r="E5" t="n">
-        <v>143719</v>
+        <v>108510</v>
       </c>
       <c r="F5" t="n">
-        <v>1672339</v>
+        <v>776488</v>
       </c>
       <c r="G5" t="n">
-        <v>9066</v>
+        <v>8891</v>
       </c>
       <c r="H5" t="n">
-        <v>29023</v>
+        <v>29019</v>
       </c>
       <c r="I5" t="n">
         <v>559</v>
@@ -1080,106 +1080,106 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>272942</v>
+        <v>261715</v>
       </c>
       <c r="L5" t="n">
-        <v>282029</v>
+        <v>278239</v>
       </c>
       <c r="M5" t="n">
-        <v>190827</v>
+        <v>155324</v>
       </c>
       <c r="N5" t="n">
-        <v>71040</v>
+        <v>45411</v>
       </c>
       <c r="O5" t="n">
-        <v>51342</v>
+        <v>50620</v>
       </c>
       <c r="P5" t="n">
-        <v>17246</v>
+        <v>15584</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999990463256836</v>
+        <v>0.9999983906745911</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9848816990852356</v>
+        <v>0.9706765413284302</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9779217839241028</v>
+        <v>0.9592379927635193</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9899507761001587</v>
+        <v>0.9832873940467834</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9972231984138489</v>
+        <v>0.9960502982139587</v>
       </c>
       <c r="V5" t="n">
-        <v>0.996726930141449</v>
+        <v>0.9936479330062866</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9990744590759277</v>
+        <v>0.9982755780220032</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15974</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169599</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19854</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58195</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>426359</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>585836</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264888</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60148</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100066</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735912084579468</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643740057945251</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838098883628845</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210225105286</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938854575157166</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983761310577393</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
@@ -1189,22 +1189,22 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>6170</v>
+        <v>6069</v>
       </c>
       <c r="E6" t="n">
-        <v>23851</v>
+        <v>18629</v>
       </c>
       <c r="F6" t="n">
-        <v>31868</v>
+        <v>12432</v>
       </c>
       <c r="G6" t="n">
-        <v>107029</v>
+        <v>43653</v>
       </c>
       <c r="H6" t="n">
-        <v>8747</v>
+        <v>7916</v>
       </c>
       <c r="I6" t="n">
-        <v>396</v>
+        <v>357</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12866</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10669</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21709</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13942</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1266,19 +1266,19 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F7" t="n">
-        <v>29647</v>
+        <v>29642</v>
       </c>
       <c r="G7" t="n">
-        <v>8883</v>
+        <v>8535</v>
       </c>
       <c r="H7" t="n">
-        <v>966416</v>
+        <v>458353</v>
       </c>
       <c r="I7" t="n">
-        <v>11983</v>
+        <v>11615</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1621</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59181</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15125</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="G8" t="n">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="H8" t="n">
-        <v>16533</v>
+        <v>14922</v>
       </c>
       <c r="I8" t="n">
-        <v>369299</v>
+        <v>177698</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
